--- a/web/files/九龙-启德-天玺．海第1期.xlsx
+++ b/web/files/九龙-启德-天玺．海第1期.xlsx
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -13653,7 +13653,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -18467,7 +18467,7 @@
           <t>A | 2141呎 (4+房)
 $13916万
 $65,000/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -18517,7 +18517,7 @@
           <t>A | 2175呎 (4+房)
 $12000万
 $55,172/呎
-(24年-07月-28日)</t>
+(24年-07月-29日)</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -18542,7 +18542,7 @@
           <t>A | 2187呎 (4+房)
 $12089万
 $55,276/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -18550,7 +18550,7 @@
           <t>B | 1408呎 (4+房)
 $6663万
 $47,325/呎
-(25年-07月-06日)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -18567,7 +18567,7 @@
           <t>A | 2194呎 (4+房)
 $11672万
 $53,200/呎
-(24年-05月-12日)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -18575,7 +18575,7 @@
           <t>B | 1408呎 (4+房)
 $7097万
 $50,407/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr"/>
@@ -18592,7 +18592,7 @@
           <t>A | 2196呎 (4+房)
 $11931万
 $54,330/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -18617,7 +18617,7 @@
           <t>A | 2192呎 (4+房)
 $11903万
 $54,300/呎
-(24年-04月-21日)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -18625,7 +18625,7 @@
           <t>B | 1408呎 (4+房)
 $6970万
 $49,500/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr"/>
@@ -18642,7 +18642,7 @@
           <t>A | 2183呎 (4+房)
 $11635万
 $53,300/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -18650,7 +18650,7 @@
           <t>B | 1408呎 (4+房)
 $6054万
 $43,000/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -18667,7 +18667,7 @@
           <t>A | 2171呎 (4+房)
 $11545万
 $53,180/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -18675,7 +18675,7 @@
           <t>B | 1408呎 (4+房)
 $5984万
 $42,500/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
@@ -18692,7 +18692,7 @@
           <t>A | 2157呎 (4+房)
 $11356万
 $52,646/呎
-(24年-06月-13日)</t>
+(24年-06月-14日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -18700,7 +18700,7 @@
           <t>B | 1408呎 (4+房)
 $7110万
 $50,497/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr"/>
@@ -18717,7 +18717,7 @@
           <t>A | 2143呎 (4+房)
 $11529万
 $53,800/呎
-(24年-07月-16日)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -18725,7 +18725,7 @@
           <t>B | 1408呎 (4+房)
 $6619万
 $47,010/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr"/>
@@ -18742,7 +18742,7 @@
           <t>A | 2129呎 (4+房)
 $10928万
 $51,329/呎
-(25年-02月-20日)</t>
+(25年-02月-21日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -18750,7 +18750,7 @@
           <t>B | 1408呎 (4+房)
 $6786万
 $48,200/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr"/>
@@ -18767,7 +18767,7 @@
           <t>A | 2115呎 (4+房)
 $10300万
 $48,700/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -18775,7 +18775,7 @@
           <t>B | 1408呎 (4+房)
 $5892万
 $41,844/呎
-(25年-07月-28日)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr"/>
@@ -18792,7 +18792,7 @@
           <t>A | 2103呎 (4+房)
 $11551万
 $54,927/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -18817,7 +18817,7 @@
           <t>A | 2096呎 (4+房)
 $12164万
 $58,033/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -18842,7 +18842,7 @@
           <t>A | 2093呎 (4+房)
 $11822万
 $56,484/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -19123,7 +19123,7 @@
           <t>A | 1104呎 (4+房)
 $3986万
 $36,101/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -19149,7 +19149,7 @@
           <t>A | 1104呎 (4+房)
 $3346万
 $30,310/呎
-(24年-05月-02日)</t>
+(24年-05月-03日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -19175,7 +19175,7 @@
           <t>A | 1104呎 (4+房)
 $3312万
 $30,000/呎
-(24年-10月-20日)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -19394,7 +19394,7 @@
           <t>A | 1104呎 (4+房)
 $3950万
 $35,779/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -19977,7 +19977,7 @@
           <t>SKY MANOR | 2191呎 (4+房)
 $14887万
 $67,946/呎
-(24年-04月-11日)</t>
+(24年-04月-12日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr"/>
@@ -19993,7 +19993,7 @@
           <t>A | 1126呎 (4+房)
 $4281万
 $38,022/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -20001,7 +20001,7 @@
           <t>B | 1089呎 (4+房)
 $4636万
 $42,571/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -20018,7 +20018,7 @@
           <t>A | 1126呎 (4+房)
 $4135万
 $36,723/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -20026,7 +20026,7 @@
           <t>B | 1089呎 (4+房)
 $3780万
 $34,711/呎
-(24年-05月-05日)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -20043,7 +20043,7 @@
           <t>A | 1126呎 (4+房)
 $4010万
 $35,613/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -20051,7 +20051,7 @@
           <t>B | 1089呎 (4+房)
 $4487万
 $41,201/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -20068,7 +20068,7 @@
           <t>A | 1126呎 (4+房)
 $4120万
 $36,590/呎
-(24年-04月-16日)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -20076,7 +20076,7 @@
           <t>B | 1089呎 (4+房)
 $3907万
 $35,875/呎
-(25年-01月-20日)</t>
+(25年-01月-21日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -20093,7 +20093,7 @@
           <t>A | 1126呎 (4+房)
 $4175万
 $37,075/呎
-(24年-04月-22日)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -20101,7 +20101,7 @@
           <t>B | 1089呎 (4+房)
 $3719万
 $34,151/呎
-(24年-12月-12日)</t>
+(24年-12月-13日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -20118,7 +20118,7 @@
           <t>A | 1126呎 (4+房)
 $4296万
 $38,156/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -20126,7 +20126,7 @@
           <t>B | 1089呎 (4+房)
 $3897万
 $35,781/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr"/>
@@ -20143,7 +20143,7 @@
           <t>A | 1126呎 (4+房)
 $4238万
 $37,638/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -20151,7 +20151,7 @@
           <t>B | 1089呎 (4+房)
 $3664万
 $33,650/呎
-(24年-12月-03日)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr"/>
@@ -20168,7 +20168,7 @@
           <t>A | 1126呎 (4+房)
 $4179万
 $37,114/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -20176,7 +20176,7 @@
           <t>B | 1089呎 (4+房)
 $3858万
 $35,425/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr"/>
@@ -20193,7 +20193,7 @@
           <t>A | 1126呎 (4+房)
 $4000万
 $35,524/呎
-(24年-04月-10日)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -20201,7 +20201,7 @@
           <t>B | 1089呎 (4+房)
 $3572万
 $32,801/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -20218,7 +20218,7 @@
           <t>A | 1126呎 (4+房)
 $4132万
 $36,701/呎
-(24年-04月-11日)</t>
+(24年-04月-12日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -20226,7 +20226,7 @@
           <t>B | 1089呎 (4+房)
 $3539万
 $32,500/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
@@ -20243,7 +20243,7 @@
           <t>A | 1126呎 (4+房)
 $3892万
 $34,563/呎
-(24年-04月-29日)</t>
+(24年-04月-30日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -20251,7 +20251,7 @@
           <t>B | 1089呎 (4+房)
 $3529万
 $32,405/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr"/>
@@ -20268,7 +20268,7 @@
           <t>A | 1126呎 (4+房)
 $3738万
 $33,197/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -20276,7 +20276,7 @@
           <t>B | 1089呎 (4+房)
 $3508万
 $32,209/呎
-(24年-07月-03日)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr"/>
@@ -20293,7 +20293,7 @@
           <t>A | 1126呎 (4+房)
 $3956万
 $35,133/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -20301,7 +20301,7 @@
           <t>B | 1089呎 (4+房)
 $3768万
 $34,601/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr"/>
@@ -20318,7 +20318,7 @@
           <t>A | 1126呎 (4+房)
 $3929万
 $34,898/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -20326,7 +20326,7 @@
           <t>B | 1089呎 (4+房)
 $3700万
 $33,976/呎
-(24年-07月-21日)</t>
+(24年-07月-22日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr"/>
@@ -20343,7 +20343,7 @@
           <t>A | 1126呎 (4+房)
 $3850万
 $34,192/呎
-(24年-06月-04日)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -20351,7 +20351,7 @@
           <t>B | 1089呎 (4+房)
 $3659万
 $33,600/呎
-(24年-04月-22日)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr"/>
@@ -20368,7 +20368,7 @@
           <t>A | 1126呎 (4+房)
 $3378万
 $30,000/呎
-(25年-01月-22日)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -20376,7 +20376,7 @@
           <t>B | 1089呎 (4+房)
 $3200万
 $29,385/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr"/>
@@ -20393,7 +20393,7 @@
           <t>A | 1126呎 (4+房)
 $3278万
 $29,115/呎
-(25年-01月-14日)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -20637,7 +20637,7 @@
           <t>SKYPLEX | 3156呎 (4+房)
 $23039万
 $73,000/呎
-(24年-04月-29日)</t>
+(24年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -20652,7 +20652,7 @@
           <t>A | 1401呎 (4+房)
 $7155万
 $51,069/呎
-(24年-11月-20日)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -20676,7 +20676,7 @@
           <t>A | 1401呎 (4+房)
 $7117万
 $50,800/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -20684,7 +20684,7 @@
           <t>B | 1366呎 (4+房)
 $6939万
 $50,800/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -20700,7 +20700,7 @@
           <t>A | 1401呎 (4+房)
 $6761万
 $48,256/呎
-(24年-04月-25日)</t>
+(24年-04月-26日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -20708,7 +20708,7 @@
           <t>B | 1366呎 (4+房)
 $6592万
 $48,256/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -20724,7 +20724,7 @@
           <t>A | 1401呎 (4+房)
 $6487万
 $46,300/呎
-(24年-04月-01日)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -20732,7 +20732,7 @@
           <t>B | 1366呎 (4+房)
 $6325万
 $46,300/呎
-(24年-04月-01日)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -20748,7 +20748,7 @@
           <t>A | 1401呎 (4+房)
 $6994万
 $49,920/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -20756,7 +20756,7 @@
           <t>B | 1366呎 (4+房)
 $6672万
 $48,842/呎
-(24年-04月-25日)</t>
+(24年-04月-26日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -20772,7 +20772,7 @@
           <t>A | 1401呎 (4+房)
 $6725万
 $48,000/呎
-(24年-04月-11日)</t>
+(24年-04月-12日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -20780,7 +20780,7 @@
           <t>B | 1366呎 (4+房)
 $6557万
 $48,000/呎
-(24年-04月-11日)</t>
+(24年-04月-12日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -20796,7 +20796,7 @@
           <t>A | 1401呎 (4+房)
 $6573万
 $46,915/呎
-(24年-04月-17日)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -20804,7 +20804,7 @@
           <t>B | 1366呎 (4+房)
 $6628万
 $48,521/呎
-(24年-04月-22日)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr"/>
@@ -20820,7 +20820,7 @@
           <t>A | 1401呎 (4+房)
 $6319万
 $45,100/呎
-(25年-05月-20日)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -20828,7 +20828,7 @@
           <t>B | 1366呎 (4+房)
 $7035万
 $51,503/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr"/>
@@ -20844,7 +20844,7 @@
           <t>A | 1401呎 (4+房)
 $6306万
 $45,007/呎
-(24年-05月-09日)</t>
+(24年-05月-10日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -20852,7 +20852,7 @@
           <t>B | 1366呎 (4+房)
 $6112万
 $44,746/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr"/>
@@ -20868,7 +20868,7 @@
           <t>A | 1401呎 (4+房)
 $6486万
 $46,298/呎
-(24年-04月-09日)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -20876,7 +20876,7 @@
           <t>B | 1366呎 (4+房)
 $6324万
 $46,298/呎
-(24年-04月-09日)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -20892,7 +20892,7 @@
           <t>A | 1401呎 (4+房)
 $6345万
 $45,291/呎
-(24年-05月-08日)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -20900,7 +20900,7 @@
           <t>B | 1366呎 (4+房)
 $6187万
 $45,291/呎
-(24年-05月-08日)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
@@ -20916,7 +20916,7 @@
           <t>A | 1401呎 (4+房)
 $5996万
 $42,800/呎
-(24年-04月-01日)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -20924,7 +20924,7 @@
           <t>B | 1366呎 (4+房)
 $7121万
 $52,128/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr"/>
@@ -20940,7 +20940,7 @@
           <t>A | 1401呎 (4+房)
 $5772万
 $41,200/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -20948,7 +20948,7 @@
           <t>B | 1366呎 (4+房)
 $6761万
 $49,492/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr"/>
@@ -20964,7 +20964,7 @@
           <t>A | 1401呎 (4+房)
 $6598万
 $47,095/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -20972,7 +20972,7 @@
           <t>B | 1366呎 (4+房)
 $6198万
 $45,375/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr"/>
@@ -20988,7 +20988,7 @@
           <t>A | 1401呎 (4+房)
 $5229万
 $37,323/呎
-(25年-06月-10日)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -20996,7 +20996,7 @@
           <t>B | 1366呎 (4+房)
 $6031万
 $44,153/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr"/>
@@ -21012,7 +21012,7 @@
           <t>A | 1401呎 (4+房)
 $6304万
 $45,000/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -21020,7 +21020,7 @@
           <t>B | 1366呎 (4+房)
 $4868万
 $35,637/呎
-(25年-04月-15日)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr"/>
@@ -21036,7 +21036,7 @@
           <t>A | 1401呎 (4+房)
 $6650万
 $47,466/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -21044,7 +21044,7 @@
           <t>B | 1366呎 (4+房)
 $6247万
 $45,731/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr"/>
@@ -21060,7 +21060,7 @@
           <t>A | 1401呎 (4+房)
 $6969万
 $49,742/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -21068,7 +21068,7 @@
           <t>B | 1366呎 (4+房)
 $6726万
 $49,239/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr"/>
@@ -21084,7 +21084,7 @@
           <t>A | 1401呎 (4+房)
 $6641万
 $47,400/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -21092,7 +21092,7 @@
           <t>B | 1366呎 (4+房)
 $6448万
 $47,200/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr"/>
@@ -21928,7 +21928,7 @@
           <t>SKY MANOR | 3099呎 (4+房)
 $24792万
 $80,000/呎
-(26年-07月-20日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr"/>

--- a/web/files/九龙-启德-天玺．海第1期.xlsx
+++ b/web/files/九龙-启德-天玺．海第1期.xlsx
@@ -133,13 +133,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -287,10 +287,10 @@
     <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -992,7 +992,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -18344,7 +18344,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18359,12 +18359,12 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -18437,12 +18437,12 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 2106呎 (4+房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -18462,7 +18462,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>A | 2141呎 (4+房)
 $13916万
@@ -18487,12 +18487,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 2144呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -18512,7 +18512,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>A | 2175呎 (4+房)
 $12000万
@@ -18520,7 +18520,7 @@
 (24年-07月-29日)</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 招标单位
@@ -18537,7 +18537,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>A | 2187呎 (4+房)
 $12089万
@@ -18545,7 +18545,7 @@
 (24年-03月-27日)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 $6663万
@@ -18562,7 +18562,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>A | 2194呎 (4+房)
 $11672万
@@ -18570,12 +18570,12 @@
 (24年-05月-13日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 $7097万
 $50,407/呎
-(26年-07月-20日)</t>
+(26年-08月-07日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr"/>
@@ -18587,7 +18587,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>A | 2196呎 (4+房)
 $11931万
@@ -18595,7 +18595,7 @@
 (24年-12月-12日)</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 招标单位
@@ -18612,7 +18612,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>A | 2192呎 (4+房)
 $11903万
@@ -18620,7 +18620,7 @@
 (24年-04月-22日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 $6970万
@@ -18637,7 +18637,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>A | 2183呎 (4+房)
 $11635万
@@ -18645,7 +18645,7 @@
 (24年-04月-18日)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 $6054万
@@ -18662,7 +18662,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>A | 2171呎 (4+房)
 $11545万
@@ -18670,7 +18670,7 @@
 (24年-11月-26日)</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 $5984万
@@ -18687,7 +18687,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>A | 2157呎 (4+房)
 $11356万
@@ -18695,12 +18695,12 @@
 (24年-06月-14日)</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 $7110万
 $50,497/呎
-(26年-07月-17日)</t>
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr"/>
@@ -18712,7 +18712,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>A | 2143呎 (4+房)
 $11529万
@@ -18720,7 +18720,7 @@
 (24年-07月-17日)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 $6619万
@@ -18737,7 +18737,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>A | 2129呎 (4+房)
 $10928万
@@ -18745,7 +18745,7 @@
 (25年-02月-21日)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 $6786万
@@ -18762,7 +18762,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>A | 2115呎 (4+房)
 $10300万
@@ -18770,7 +18770,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 $5892万
@@ -18787,7 +18787,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>A | 2103呎 (4+房)
 $11551万
@@ -18812,7 +18812,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>A | 2096呎 (4+房)
 $12164万
@@ -18820,7 +18820,7 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 招标单位
@@ -18837,7 +18837,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>A | 2093呎 (4+房)
 $11822万
@@ -18862,7 +18862,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 2093呎 (4+房)
 招标单位
@@ -18870,7 +18870,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
 招标单位
@@ -18887,12 +18887,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 2093呎 (4+房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -18912,12 +18912,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 2093呎 (4+房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -19118,12 +19118,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 $3986万
 $36,101/呎
-(26年-07月-13日)</t>
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -19144,7 +19144,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 $3346万
@@ -19170,7 +19170,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 $3312万
@@ -19214,7 +19214,7 @@
       </c>
       <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="24" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>SKY MANOR | 998呎 (3房)
 招标单位
@@ -19229,7 +19229,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 招标单位
@@ -19389,7 +19389,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 $3950万
@@ -19469,7 +19469,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 招标单位
@@ -19549,7 +19549,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 招标单位
@@ -19972,7 +19972,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr"/>
       <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>SKY MANOR | 2191呎 (4+房)
 $14887万
@@ -19988,7 +19988,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $4281万
@@ -19996,7 +19996,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $4636万
@@ -20013,7 +20013,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $4135万
@@ -20021,7 +20021,7 @@
 (24年-03月-28日)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $3780万
@@ -20038,7 +20038,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $4010万
@@ -20046,7 +20046,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $4487万
@@ -20063,7 +20063,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $4120万
@@ -20071,7 +20071,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $3907万
@@ -20088,7 +20088,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $4175万
@@ -20096,7 +20096,7 @@
 (24年-04月-23日)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $3719万
@@ -20113,7 +20113,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $4296万
@@ -20121,7 +20121,7 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $3897万
@@ -20138,7 +20138,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $4238万
@@ -20146,7 +20146,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $3664万
@@ -20163,7 +20163,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $4179万
@@ -20171,7 +20171,7 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $3858万
@@ -20188,7 +20188,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $4000万
@@ -20196,7 +20196,7 @@
 (24年-04月-11日)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $3572万
@@ -20213,7 +20213,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $4132万
@@ -20221,7 +20221,7 @@
 (24年-04月-12日)</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $3539万
@@ -20238,7 +20238,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $3892万
@@ -20246,7 +20246,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $3529万
@@ -20263,7 +20263,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $3738万
@@ -20271,7 +20271,7 @@
 (24年-04月-18日)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $3508万
@@ -20288,7 +20288,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $3956万
@@ -20296,7 +20296,7 @@
 (24年-04月-16日)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $3768万
@@ -20313,7 +20313,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $3929万
@@ -20321,7 +20321,7 @@
 (24年-04月-16日)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $3700万
@@ -20338,7 +20338,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $3850万
@@ -20346,7 +20346,7 @@
 (24年-06月-05日)</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $3659万
@@ -20363,7 +20363,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $3378万
@@ -20371,7 +20371,7 @@
 (25年-01月-23日)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 $3200万
@@ -20388,7 +20388,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>A | 1126呎 (4+房)
 $3278万
@@ -20396,7 +20396,7 @@
 (25年-01月-15日)</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 1089呎 (4+房)
 招标单位
@@ -20632,7 +20632,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>SKYPLEX | 3156呎 (4+房)
 $23039万
@@ -20647,7 +20647,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $7155万
@@ -20671,7 +20671,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $7117万
@@ -20679,7 +20679,7 @@
 (24年-04月-16日)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6939万
@@ -20695,7 +20695,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $6761万
@@ -20703,7 +20703,7 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6592万
@@ -20719,7 +20719,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $6487万
@@ -20727,7 +20727,7 @@
 (24年-04月-02日)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6325万
@@ -20743,7 +20743,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $6994万
@@ -20751,7 +20751,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6672万
@@ -20767,7 +20767,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $6725万
@@ -20775,7 +20775,7 @@
 (24年-04月-12日)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6557万
@@ -20791,7 +20791,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $6573万
@@ -20799,7 +20799,7 @@
 (24年-04月-18日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6628万
@@ -20815,7 +20815,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $6319万
@@ -20823,7 +20823,7 @@
 (25年-05月-21日)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $7035万
@@ -20839,7 +20839,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $6306万
@@ -20847,7 +20847,7 @@
 (24年-05月-10日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6112万
@@ -20863,7 +20863,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $6486万
@@ -20871,7 +20871,7 @@
 (24年-04月-10日)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6324万
@@ -20887,7 +20887,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $6345万
@@ -20895,7 +20895,7 @@
 (24年-05月-09日)</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6187万
@@ -20911,7 +20911,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $5996万
@@ -20919,7 +20919,7 @@
 (24年-04月-02日)</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $7121万
@@ -20935,7 +20935,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $5772万
@@ -20943,7 +20943,7 @@
 (24年-10月-24日)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6761万
@@ -20959,7 +20959,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $6598万
@@ -20967,7 +20967,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6198万
@@ -20983,7 +20983,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $5229万
@@ -20991,7 +20991,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6031万
@@ -21007,7 +21007,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $6304万
@@ -21015,7 +21015,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $4868万
@@ -21031,7 +21031,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $6650万
@@ -21039,7 +21039,7 @@
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6247万
@@ -21055,7 +21055,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $6969万
@@ -21063,7 +21063,7 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6726万
@@ -21079,7 +21079,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>A | 1401呎 (4+房)
 $6641万
@@ -21087,7 +21087,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
 $6448万
@@ -21923,7 +21923,7 @@
           <t>2&amp;3</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>SKY MANOR | 3099呎 (4+房)
 $24792万

--- a/web/files/九龙-启德-天玺．海第1期.xlsx
+++ b/web/files/九龙-启德-天玺．海第1期.xlsx
@@ -2934,23 +2934,19 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>64000000</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>45455</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2959,12 +2955,12 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -2974,7 +2970,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18344,7 +18340,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18354,7 +18350,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18820,12 +18816,12 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>B | 1408呎 (4+房)
-招标单位
--
-(在售)</t>
+$6400万
+$45,455/呎
+(26年-08月-16日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr"/>

--- a/web/files/九龙-启德-天玺．海第1期.xlsx
+++ b/web/files/九龙-启德-天玺．海第1期.xlsx
@@ -2939,7 +2939,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -18821,7 +18821,7 @@
           <t>B | 1408呎 (4+房)
 $6400万
 $45,455/呎
-(26年-08月-16日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr"/>
